--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.1037037037037037</v>
+        <v>0.08270676691729323</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.1197183098591549</v>
+        <v>0.1126760563380282</v>
       </c>
       <c r="D2">
-        <v>0.8992805755395683</v>
+        <v>0.9197080291970803</v>
       </c>
       <c r="E2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F2">
         <v>4</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.08270676691729323</v>
+        <v>0.09022556390977443</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.1126760563380282</v>
+        <v>0.1267605633802817</v>
       </c>
       <c r="D2">
-        <v>0.9197080291970803</v>
+        <v>0.9117647058823529</v>
       </c>
       <c r="E2">
         <v>133</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
